--- a/data/Ascona/cost/cost_report.xlsx
+++ b/data/Ascona/cost/cost_report.xlsx
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>337.8384526004675</v>
+        <v>1746.313173183486</v>
       </c>
       <c r="C2" t="n">
-        <v>5945.647080950263</v>
+        <v>14641.52920927986</v>
       </c>
       <c r="D2" t="n">
-        <v>11462.66329699787</v>
+        <v>57414.03182712485</v>
       </c>
       <c r="E2" t="n">
-        <v>1275.025676759716</v>
+        <v>4196.282908293487</v>
       </c>
       <c r="F2" t="n">
-        <v>11925.86722305355</v>
+        <v>18874.81767570824</v>
       </c>
       <c r="G2" t="n">
-        <v>30947.04173036187</v>
+        <v>96872.97479358992</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.02618627701687</v>
+        <v>0.08197043761066296</v>
       </c>
     </row>
     <row r="3">
@@ -515,22 +515,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>337.8386706937439</v>
+        <v>1747.556196067624</v>
       </c>
       <c r="C3" t="n">
-        <v>5823.51348064833</v>
+        <v>14467.62885939126</v>
       </c>
       <c r="D3" t="n">
-        <v>11777.43217331136</v>
+        <v>58140.63676231453</v>
       </c>
       <c r="E3" t="n">
-        <v>1296.079795066624</v>
+        <v>4087.829696731932</v>
       </c>
       <c r="F3" t="n">
-        <v>12276.91658391796</v>
+        <v>19907.17761651759</v>
       </c>
       <c r="G3" t="n">
-        <v>31511.78070363802</v>
+        <v>98350.82913102294</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.02666413888571297</v>
+        <v>0.08322094495827273</v>
       </c>
     </row>
     <row r="4">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>337.8590537281266</v>
+        <v>1746.313173183486</v>
       </c>
       <c r="C4" t="n">
-        <v>5282.483521803108</v>
+        <v>14623.92328608379</v>
       </c>
       <c r="D4" t="n">
-        <v>14081.46441075925</v>
+        <v>57504.1263699386</v>
       </c>
       <c r="E4" t="n">
-        <v>1270.705291458977</v>
+        <v>4196.282908293489</v>
       </c>
       <c r="F4" t="n">
-        <v>10278.11970093072</v>
+        <v>18828.13237174009</v>
       </c>
       <c r="G4" t="n">
-        <v>31250.63197868018</v>
+        <v>96898.77810923946</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.02644316419889373</v>
+        <v>0.08199227145111335</v>
       </c>
     </row>
     <row r="5">
@@ -581,22 +581,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>337.8590537281266</v>
+        <v>1747.556196067624</v>
       </c>
       <c r="C5" t="n">
-        <v>5158.296746892899</v>
+        <v>14450.02293619519</v>
       </c>
       <c r="D5" t="n">
-        <v>14394.2157663444</v>
+        <v>58230.73130502766</v>
       </c>
       <c r="E5" t="n">
-        <v>1293.929384229356</v>
+        <v>4087.829696731931</v>
       </c>
       <c r="F5" t="n">
-        <v>10630.96283437528</v>
+        <v>19860.49231254944</v>
       </c>
       <c r="G5" t="n">
-        <v>31815.26378557006</v>
+        <v>98376.63244657184</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.0269209353873834</v>
+        <v>0.08324277879863796</v>
       </c>
     </row>
   </sheetData>

--- a/data/Ascona/cost/cost_report.xlsx
+++ b/data/Ascona/cost/cost_report.xlsx
@@ -482,30 +482,30 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1746.313173183486</v>
+        <v>1814.255155507688</v>
       </c>
       <c r="C2" t="n">
-        <v>14641.52920927986</v>
+        <v>16879.30937828685</v>
       </c>
       <c r="D2" t="n">
-        <v>57414.03182712485</v>
+        <v>87177.68678703241</v>
       </c>
       <c r="E2" t="n">
-        <v>4196.282908293487</v>
+        <v>5819.535168348516</v>
       </c>
       <c r="F2" t="n">
-        <v>18874.81767570824</v>
+        <v>37577.54230734662</v>
       </c>
       <c r="G2" t="n">
-        <v>96872.97479358992</v>
+        <v>149268.3287965221</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.08197043761066296</v>
+        <v>0.1262539442314415</v>
       </c>
     </row>
     <row r="3">
@@ -515,30 +515,30 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1747.556196067624</v>
+        <v>1813.706076635944</v>
       </c>
       <c r="C3" t="n">
-        <v>14467.62885939126</v>
+        <v>17092.94676354963</v>
       </c>
       <c r="D3" t="n">
-        <v>58140.63676231453</v>
+        <v>86610.6919353409</v>
       </c>
       <c r="E3" t="n">
-        <v>4087.829696731932</v>
+        <v>5770.320426471721</v>
       </c>
       <c r="F3" t="n">
-        <v>19907.17761651759</v>
+        <v>34848.6608327119</v>
       </c>
       <c r="G3" t="n">
-        <v>98350.82913102294</v>
+        <v>146136.3260347101</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>cp_dr</t>
+          <t>base</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.08322094495827273</v>
+        <v>0.1236048377182871</v>
       </c>
     </row>
     <row r="4">
@@ -548,30 +548,30 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1746.313173183486</v>
+        <v>1814.255155507688</v>
       </c>
       <c r="C4" t="n">
-        <v>14623.92328608379</v>
+        <v>17173.30267127711</v>
       </c>
       <c r="D4" t="n">
-        <v>57504.1263699386</v>
+        <v>86598.31668408834</v>
       </c>
       <c r="E4" t="n">
-        <v>4196.282908293489</v>
+        <v>5675.000180920087</v>
       </c>
       <c r="F4" t="n">
-        <v>18828.13237174009</v>
+        <v>37826.41542954942</v>
       </c>
       <c r="G4" t="n">
-        <v>96898.77810923946</v>
+        <v>149087.2901213426</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>cp_cu</t>
+          <t>cp_dr</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.08199227145111335</v>
+        <v>0.126100818334045</v>
       </c>
     </row>
     <row r="5">
@@ -581,30 +581,30 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1747.556196067624</v>
+        <v>1813.706076635944</v>
       </c>
       <c r="C5" t="n">
-        <v>14450.02293619519</v>
+        <v>16801.84402954219</v>
       </c>
       <c r="D5" t="n">
-        <v>58230.73130502766</v>
+        <v>86886.25402574176</v>
       </c>
       <c r="E5" t="n">
-        <v>4087.829696731931</v>
+        <v>5880.421777796133</v>
       </c>
       <c r="F5" t="n">
-        <v>19860.49231254944</v>
+        <v>34937.74307166549</v>
       </c>
       <c r="G5" t="n">
-        <v>98376.63244657184</v>
+        <v>146319.9689813815</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cp_cu</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.08324277879863796</v>
+        <v>0.1237601663572187</v>
       </c>
     </row>
   </sheetData>

--- a/data/Ascona/cost/cost_report.xlsx
+++ b/data/Ascona/cost/cost_report.xlsx
@@ -482,30 +482,30 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1814.255155507688</v>
+        <v>1697.056783273779</v>
       </c>
       <c r="C2" t="n">
-        <v>16879.30937828685</v>
+        <v>16381.01865095532</v>
       </c>
       <c r="D2" t="n">
-        <v>87177.68678703241</v>
+        <v>95797.84291042251</v>
       </c>
       <c r="E2" t="n">
-        <v>5819.535168348516</v>
+        <v>4471.062118281722</v>
       </c>
       <c r="F2" t="n">
-        <v>37577.54230734662</v>
+        <v>31192.48706291146</v>
       </c>
       <c r="G2" t="n">
-        <v>149268.3287965221</v>
+        <v>149539.4675258448</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>base</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.1262539442314415</v>
+        <v>0.1264832784397554</v>
       </c>
     </row>
     <row r="3">
@@ -515,30 +515,30 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1813.706076635944</v>
+        <v>1716.840659831052</v>
       </c>
       <c r="C3" t="n">
-        <v>17092.94676354963</v>
+        <v>16424.37835953316</v>
       </c>
       <c r="D3" t="n">
-        <v>86610.6919353409</v>
+        <v>96231.78517341899</v>
       </c>
       <c r="E3" t="n">
-        <v>5770.320426471721</v>
+        <v>4478.770110369387</v>
       </c>
       <c r="F3" t="n">
-        <v>34848.6608327119</v>
+        <v>33615.48447962834</v>
       </c>
       <c r="G3" t="n">
-        <v>146136.3260347101</v>
+        <v>152467.2587827809</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.1236048377182871</v>
+        <v>0.1289596590427593</v>
       </c>
     </row>
     <row r="4">
@@ -548,30 +548,30 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1814.255155507688</v>
+        <v>1697.056783273777</v>
       </c>
       <c r="C4" t="n">
-        <v>17173.30267127711</v>
+        <v>16354.19830337027</v>
       </c>
       <c r="D4" t="n">
-        <v>86598.31668408834</v>
+        <v>96025.10652458566</v>
       </c>
       <c r="E4" t="n">
-        <v>5675.000180920087</v>
+        <v>4471.062118281722</v>
       </c>
       <c r="F4" t="n">
-        <v>37826.41542954942</v>
+        <v>31101.75306975448</v>
       </c>
       <c r="G4" t="n">
-        <v>149087.2901213426</v>
+        <v>149649.1767992659</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>cp_dr</t>
+          <t>cp_cu</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.126100818334045</v>
+        <v>0.1265760725950854</v>
       </c>
     </row>
     <row r="5">
@@ -581,30 +581,30 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1813.706076635944</v>
+        <v>1716.840659831054</v>
       </c>
       <c r="C5" t="n">
-        <v>16801.84402954219</v>
+        <v>16481.42558866963</v>
       </c>
       <c r="D5" t="n">
-        <v>86886.25402574176</v>
+        <v>95785.75160201702</v>
       </c>
       <c r="E5" t="n">
-        <v>5880.421777796133</v>
+        <v>4478.770110369389</v>
       </c>
       <c r="F5" t="n">
-        <v>34937.74307166549</v>
+        <v>33888.90639115355</v>
       </c>
       <c r="G5" t="n">
-        <v>146319.9689813815</v>
+        <v>152351.6943520406</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>cp_cu</t>
+          <t>cp_dr</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.1237601663572187</v>
+        <v>0.128861912485861</v>
       </c>
     </row>
   </sheetData>
